--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prestamour\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7AD7B0E-32D8-43E0-9BAB-17B4E0AAD6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980CD9CA-01CC-494A-B658-6659E3A635E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{91893823-09B1-45BF-B334-EEE7F4E1D62D}"/>
   </bookViews>
